--- a/exports/trend_1d/GODREJCP_full_report.xlsx
+++ b/exports/trend_1d/GODREJCP_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>7.39</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42089</v>
+        <v>42090</v>
       </c>
       <c r="H2" t="n">
-        <v>357.92</v>
+        <v>352.3</v>
       </c>
       <c r="I2" t="n">
         <v>355.3170531652751</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K2" t="n">
-        <v>0.42</v>
+        <v>-1.16</v>
       </c>
       <c r="L2" t="n">
         <v>4.4</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>13.44</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42103</v>
+        <v>42104</v>
       </c>
       <c r="H3" t="n">
-        <v>389.2</v>
+        <v>398.87</v>
       </c>
       <c r="I3" t="n">
         <v>392.9220872286655</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>-10.47</v>
+        <v>-13.22</v>
       </c>
       <c r="L3" t="n">
-        <v>12.09</v>
+        <v>14.83</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>13.9</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42123</v>
+        <v>42124</v>
       </c>
       <c r="H4" t="n">
-        <v>360.17</v>
+        <v>350.59</v>
       </c>
       <c r="I4" t="n">
         <v>356.5284988179997</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>-9.699999999999999</v>
+        <v>-12.1</v>
       </c>
       <c r="L4" t="n">
         <v>14.76</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>15.75</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42139</v>
+        <v>42142</v>
       </c>
       <c r="H5" t="n">
-        <v>388.67</v>
+        <v>399.63</v>
       </c>
       <c r="I5" t="n">
         <v>398.316620933804</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K5" t="n">
-        <v>-10.86</v>
+        <v>-13.99</v>
       </c>
       <c r="L5" t="n">
-        <v>11.49</v>
+        <v>16.01</v>
       </c>
       <c r="M5" t="n">
         <v>0.97</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>13.13</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H6" t="n">
-        <v>435.6</v>
+        <v>407.32</v>
       </c>
       <c r="I6" t="n">
         <v>417.7349200641404</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K6" t="n">
-        <v>9</v>
+        <v>1.92</v>
       </c>
       <c r="L6" t="n">
         <v>13.5</v>
@@ -783,7 +854,7 @@
         <v>3.67</v>
       </c>
       <c r="N6" t="n">
-        <v>4.51</v>
+        <v>6.49</v>
       </c>
       <c r="O6" t="n">
         <v>2.82</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>17.47</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42314</v>
+        <v>42317</v>
       </c>
       <c r="H7" t="n">
-        <v>434.3</v>
+        <v>450.55</v>
       </c>
       <c r="I7" t="n">
         <v>444.1002406584925</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.62</v>
+        <v>-10.61</v>
       </c>
       <c r="L7" t="n">
         <v>15.38</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>14.11</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42384</v>
+        <v>42387</v>
       </c>
       <c r="H8" t="n">
-        <v>413.5</v>
+        <v>403.53</v>
       </c>
       <c r="I8" t="n">
         <v>405.1322613879581</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.220000000000001</v>
+        <v>-10.44</v>
       </c>
       <c r="L8" t="n">
         <v>11.22</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>12.96</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42439</v>
+        <v>42440</v>
       </c>
       <c r="H9" t="n">
-        <v>416.59</v>
+        <v>433.47</v>
       </c>
       <c r="I9" t="n">
         <v>424.3976832334054</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.24</v>
+        <v>-7.42</v>
       </c>
       <c r="L9" t="n">
-        <v>5.69</v>
+        <v>7.8</v>
       </c>
       <c r="M9" t="n">
         <v>2.12</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.8</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42591</v>
+        <v>42592</v>
       </c>
       <c r="H10" t="n">
-        <v>510</v>
+        <v>500.63</v>
       </c>
       <c r="I10" t="n">
         <v>509.8851064078347</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K10" t="n">
-        <v>17.66</v>
+        <v>15.49</v>
       </c>
       <c r="L10" t="n">
         <v>4.04</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42619</v>
+        <v>42620</v>
       </c>
       <c r="H11" t="n">
-        <v>541.02</v>
+        <v>556.63</v>
       </c>
       <c r="I11" t="n">
         <v>542.4481922082521</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K11" t="n">
-        <v>-8.07</v>
+        <v>-11.19</v>
       </c>
       <c r="L11" t="n">
-        <v>8.52</v>
+        <v>12.19</v>
       </c>
       <c r="M11" t="n">
         <v>0.96</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>9.07</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42676</v>
+        <v>42677</v>
       </c>
       <c r="H12" t="n">
-        <v>521.02</v>
+        <v>511.77</v>
       </c>
       <c r="I12" t="n">
         <v>519.3623066035767</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K12" t="n">
-        <v>-6.4</v>
+        <v>-8.06</v>
       </c>
       <c r="L12" t="n">
-        <v>7.42</v>
+        <v>8.31</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.59</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42741</v>
+        <v>42744</v>
       </c>
       <c r="H13" t="n">
-        <v>507.43</v>
+        <v>513.4</v>
       </c>
       <c r="I13" t="n">
         <v>513.1430825759739</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K13" t="n">
-        <v>0.85</v>
+        <v>-0.32</v>
       </c>
       <c r="L13" t="n">
         <v>2.23</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>7.52</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42947</v>
+        <v>42948</v>
       </c>
       <c r="H14" t="n">
-        <v>691.5</v>
+        <v>642.9299999999999</v>
       </c>
       <c r="I14" t="n">
         <v>653.5787417252506</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K14" t="n">
-        <v>34.69</v>
+        <v>25.23</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>1.36</v>
+        <v>2.63</v>
       </c>
       <c r="N14" t="n">
-        <v>4.21</v>
+        <v>7.02</v>
       </c>
       <c r="O14" t="n">
         <v>1.18</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>13.21</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43014</v>
+        <v>43017</v>
       </c>
       <c r="H15" t="n">
-        <v>631.9</v>
+        <v>654.13</v>
       </c>
       <c r="I15" t="n">
         <v>649.7473521324054</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K15" t="n">
-        <v>1.72</v>
+        <v>-1.74</v>
       </c>
       <c r="L15" t="n">
         <v>5.77</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>9.84</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43136</v>
+        <v>43137</v>
       </c>
       <c r="H16" t="n">
-        <v>692.67</v>
+        <v>672.4</v>
       </c>
       <c r="I16" t="n">
         <v>672.9097528266917</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K16" t="n">
-        <v>5.89</v>
+        <v>2.79</v>
       </c>
       <c r="L16" t="n">
         <v>8.23</v>
       </c>
       <c r="M16" t="n">
-        <v>0.93</v>
+        <v>2.79</v>
       </c>
       <c r="N16" t="n">
         <v>3.81</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>9.31</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43182</v>
+        <v>43185</v>
       </c>
       <c r="H17" t="n">
-        <v>729.9299999999999</v>
+        <v>735.4299999999999</v>
       </c>
       <c r="I17" t="n">
         <v>734.5909147725513</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K17" t="n">
-        <v>-8.56</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>10.82</v>
+        <v>11.55</v>
       </c>
       <c r="M17" t="n">
         <v>1.18</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.27</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43347</v>
+        <v>43348</v>
       </c>
       <c r="H18" t="n">
-        <v>932.77</v>
+        <v>896.77</v>
       </c>
       <c r="I18" t="n">
         <v>897.0576704117721</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K18" t="n">
-        <v>26.83</v>
+        <v>21.94</v>
       </c>
       <c r="L18" t="n">
         <v>3.64</v>
@@ -1467,7 +1682,7 @@
         <v>0.92</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>3.86</v>
       </c>
       <c r="O18" t="n">
         <v>0.75</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>10.6</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43434</v>
+        <v>43437</v>
       </c>
       <c r="H19" t="n">
-        <v>750.35</v>
+        <v>771.4</v>
       </c>
       <c r="I19" t="n">
         <v>769.223480740039</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K19" t="n">
-        <v>16.33</v>
+        <v>13.98</v>
       </c>
       <c r="L19" t="n">
         <v>3.96</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43490</v>
+        <v>43493</v>
       </c>
       <c r="H20" t="n">
-        <v>780.3</v>
+        <v>759.25</v>
       </c>
       <c r="I20" t="n">
         <v>765.1432315344679</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K20" t="n">
-        <v>1.15</v>
+        <v>-1.58</v>
       </c>
       <c r="L20" t="n">
         <v>5.59</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>10.23</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43532</v>
+        <v>43535</v>
       </c>
       <c r="H21" t="n">
-        <v>708</v>
+        <v>722.75</v>
       </c>
       <c r="I21" t="n">
         <v>711.9684805309302</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K21" t="n">
-        <v>6.75</v>
+        <v>4.81</v>
       </c>
       <c r="L21" t="n">
         <v>3.65</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>7.78</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43553</v>
+        <v>43556</v>
       </c>
       <c r="H22" t="n">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="I22" t="n">
         <v>678.0686072500556</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.08</v>
+        <v>-6.33</v>
       </c>
       <c r="L22" t="n">
-        <v>5.85</v>
+        <v>6.58</v>
       </c>
       <c r="M22" t="n">
         <v>0.57</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43615</v>
+        <v>43616</v>
       </c>
       <c r="H23" t="n">
-        <v>658.45</v>
+        <v>688.05</v>
       </c>
       <c r="I23" t="n">
         <v>679.502163966557</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K23" t="n">
-        <v>2.74</v>
+        <v>-1.63</v>
       </c>
       <c r="L23" t="n">
         <v>2.33</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>9.68</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H24" t="n">
-        <v>671.85</v>
+        <v>651.5</v>
       </c>
       <c r="I24" t="n">
         <v>654.0077604044295</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.35</v>
+        <v>-5.31</v>
       </c>
       <c r="L24" t="n">
-        <v>5.88</v>
+        <v>5.94</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="N24" t="n">
-        <v>2.42</v>
+        <v>3.03</v>
       </c>
       <c r="O24" t="n">
         <v>4.5</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>8.19</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43685</v>
+        <v>43686</v>
       </c>
       <c r="H25" t="n">
-        <v>642.8</v>
+        <v>653.4</v>
       </c>
       <c r="I25" t="n">
         <v>649.108997161405</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K25" t="n">
-        <v>1.34</v>
+        <v>-0.29</v>
       </c>
       <c r="L25" t="n">
         <v>2.32</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>8.74</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43711</v>
+        <v>43712</v>
       </c>
       <c r="H26" t="n">
-        <v>599.75</v>
+        <v>582.9</v>
       </c>
       <c r="I26" t="n">
         <v>596.3071677580911</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K26" t="n">
-        <v>-8.210000000000001</v>
+        <v>-10.79</v>
       </c>
       <c r="L26" t="n">
-        <v>10.31</v>
+        <v>12</v>
       </c>
       <c r="M26" t="n">
         <v>0.7</v>
       </c>
       <c r="N26" t="n">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="O26" t="n">
         <v>1.65</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>11.69</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43726</v>
+        <v>43727</v>
       </c>
       <c r="H27" t="n">
-        <v>649.25</v>
+        <v>655.6</v>
       </c>
       <c r="I27" t="n">
         <v>649.6239474171954</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K27" t="n">
-        <v>-11.38</v>
+        <v>-12.47</v>
       </c>
       <c r="L27" t="n">
-        <v>13.57</v>
+        <v>14.55</v>
       </c>
       <c r="M27" t="n">
         <v>1.49</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43803</v>
+        <v>43804</v>
       </c>
       <c r="H28" t="n">
-        <v>695.7</v>
+        <v>671.8</v>
       </c>
       <c r="I28" t="n">
         <v>687.0622777756749</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K28" t="n">
-        <v>6.12</v>
+        <v>2.47</v>
       </c>
       <c r="L28" t="n">
         <v>1.18</v>
@@ -2037,7 +2372,7 @@
         <v>0.96</v>
       </c>
       <c r="N28" t="n">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="O28" t="n">
         <v>0.98</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>11.5</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43838</v>
+        <v>43839</v>
       </c>
       <c r="H29" t="n">
-        <v>712.15</v>
+        <v>724.4</v>
       </c>
       <c r="I29" t="n">
         <v>718.51338555318</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K29" t="n">
-        <v>-6.01</v>
+        <v>-7.83</v>
       </c>
       <c r="L29" t="n">
-        <v>6.58</v>
+        <v>7.96</v>
       </c>
       <c r="M29" t="n">
         <v>0.62</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>7.36</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43859</v>
+        <v>43860</v>
       </c>
       <c r="H30" t="n">
-        <v>740.85</v>
+        <v>683.5</v>
       </c>
       <c r="I30" t="n">
         <v>707.7542795052523</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K30" t="n">
+        <v>-5.65</v>
+      </c>
+      <c r="L30" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="M30" t="n">
         <v>2.27</v>
       </c>
-      <c r="L30" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.3</v>
-      </c>
       <c r="N30" t="n">
-        <v>2.27</v>
+        <v>7.74</v>
       </c>
       <c r="O30" t="n">
         <v>1.72</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>13.11</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43894</v>
+        <v>43895</v>
       </c>
       <c r="H31" t="n">
-        <v>631.75</v>
+        <v>650.65</v>
       </c>
       <c r="I31" t="n">
         <v>634.1995231834957</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K31" t="n">
-        <v>7.57</v>
+        <v>4.81</v>
       </c>
       <c r="L31" t="n">
         <v>6.92</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>11.9</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43901</v>
+        <v>43902</v>
       </c>
       <c r="H32" t="n">
-        <v>607.4</v>
+        <v>560.2</v>
       </c>
       <c r="I32" t="n">
         <v>573.2455178393085</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K32" t="n">
-        <v>-6.65</v>
+        <v>-13.9</v>
       </c>
       <c r="L32" t="n">
-        <v>7.45</v>
+        <v>16.48</v>
       </c>
       <c r="M32" t="n">
         <v>3.34</v>
       </c>
       <c r="N32" t="n">
-        <v>3.93</v>
+        <v>7.77</v>
       </c>
       <c r="O32" t="n">
         <v>2.99</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>17.29</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43928</v>
+        <v>43929</v>
       </c>
       <c r="H33" t="n">
-        <v>558.85</v>
+        <v>600</v>
       </c>
       <c r="I33" t="n">
         <v>574.1167853320854</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K33" t="n">
-        <v>0.24</v>
+        <v>-7.1</v>
       </c>
       <c r="L33" t="n">
-        <v>6.21</v>
+        <v>12.27</v>
       </c>
       <c r="M33" t="n">
         <v>3.67</v>
       </c>
       <c r="N33" t="n">
-        <v>6.39</v>
+        <v>7.36</v>
       </c>
       <c r="O33" t="n">
         <v>-7.77</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>21.8</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44071</v>
+        <v>44074</v>
       </c>
       <c r="H34" t="n">
-        <v>670.95</v>
+        <v>651.3</v>
       </c>
       <c r="I34" t="n">
         <v>652.3370766191301</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K34" t="n">
-        <v>11.83</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L34" t="n">
         <v>19.32</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>9.81</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44090</v>
+        <v>44091</v>
       </c>
       <c r="H35" t="n">
-        <v>707.4</v>
+        <v>709.2</v>
       </c>
       <c r="I35" t="n">
         <v>708.1164181341003</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K35" t="n">
-        <v>-8.609999999999999</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>9.470000000000001</v>
+        <v>10.99</v>
       </c>
       <c r="M35" t="n">
         <v>0.89</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>7.56</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44119</v>
+        <v>44120</v>
       </c>
       <c r="H36" t="n">
-        <v>682.15</v>
+        <v>677.85</v>
       </c>
       <c r="I36" t="n">
         <v>678.0655273869324</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.81</v>
+        <v>-4.42</v>
       </c>
       <c r="L36" t="n">
         <v>6.09</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>10.28</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44174</v>
+        <v>44175</v>
       </c>
       <c r="H37" t="n">
-        <v>704.95</v>
+        <v>728.55</v>
       </c>
       <c r="I37" t="n">
         <v>723.5856681479697</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K37" t="n">
-        <v>-4</v>
+        <v>-7.48</v>
       </c>
       <c r="L37" t="n">
-        <v>6.96</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M37" t="n">
         <v>1.75</v>
       </c>
       <c r="N37" t="n">
-        <v>2.81</v>
+        <v>3.35</v>
       </c>
       <c r="O37" t="n">
         <v>-0.63</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>8.84</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44232</v>
+        <v>44235</v>
       </c>
       <c r="H38" t="n">
-        <v>749.15</v>
+        <v>735.4</v>
       </c>
       <c r="I38" t="n">
         <v>739.1127372516281</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K38" t="n">
-        <v>2.83</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L38" t="n">
         <v>6.24</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>10.98</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44280</v>
+        <v>44281</v>
       </c>
       <c r="H39" t="n">
-        <v>679.8</v>
+        <v>710.25</v>
       </c>
       <c r="I39" t="n">
         <v>708.2589382876458</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K39" t="n">
-        <v>7.56</v>
+        <v>3.42</v>
       </c>
       <c r="L39" t="n">
         <v>4.03</v>
       </c>
       <c r="M39" t="n">
-        <v>0.91</v>
+        <v>2.06</v>
       </c>
       <c r="N39" t="n">
-        <v>3.25</v>
+        <v>4.48</v>
       </c>
       <c r="O39" t="n">
         <v>-1.84</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>9.27</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44463</v>
+        <v>44466</v>
       </c>
       <c r="H40" t="n">
-        <v>1041.65</v>
+        <v>1038.7</v>
       </c>
       <c r="I40" t="n">
         <v>1041.494083234357</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K40" t="n">
-        <v>46.66</v>
+        <v>46.24</v>
       </c>
       <c r="L40" t="n">
         <v>3.2</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>7.45</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44552</v>
+        <v>44553</v>
       </c>
       <c r="H41" t="n">
-        <v>958.15</v>
+        <v>964.8</v>
       </c>
       <c r="I41" t="n">
         <v>960.2238782630639</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K41" t="n">
-        <v>7.75</v>
+        <v>7.11</v>
       </c>
       <c r="L41" t="n">
         <v>6.14</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>9.08</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44581</v>
+        <v>44582</v>
       </c>
       <c r="H42" t="n">
-        <v>902.75</v>
+        <v>891.2</v>
       </c>
       <c r="I42" t="n">
         <v>898.6303634375226</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K42" t="n">
-        <v>-6.43</v>
+        <v>-7.63</v>
       </c>
       <c r="L42" t="n">
-        <v>6.69</v>
+        <v>8.41</v>
       </c>
       <c r="M42" t="n">
         <v>1.38</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>7.79</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44652</v>
+        <v>44655</v>
       </c>
       <c r="H43" t="n">
-        <v>753</v>
+        <v>770.65</v>
       </c>
       <c r="I43" t="n">
         <v>760.0140995043861</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K43" t="n">
-        <v>15.51</v>
+        <v>13.53</v>
       </c>
       <c r="L43" t="n">
         <v>4.3</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>10.53</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44725</v>
+        <v>44726</v>
       </c>
       <c r="H44" t="n">
-        <v>738.3</v>
+        <v>737.1</v>
       </c>
       <c r="I44" t="n">
         <v>738.1384396141895</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K44" t="n">
-        <v>-4.2</v>
+        <v>-4.35</v>
       </c>
       <c r="L44" t="n">
-        <v>4.69</v>
+        <v>4.92</v>
       </c>
       <c r="M44" t="n">
         <v>3.9</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>8.4</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44735</v>
+        <v>44736</v>
       </c>
       <c r="H45" t="n">
-        <v>774.8</v>
+        <v>794.55</v>
       </c>
       <c r="I45" t="n">
         <v>788.4519627545386</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.11</v>
+        <v>-7.79</v>
       </c>
       <c r="L45" t="n">
-        <v>6.3</v>
+        <v>8.07</v>
       </c>
       <c r="M45" t="n">
         <v>0.8</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>10.64</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H46" t="n">
-        <v>890.45</v>
+        <v>871.75</v>
       </c>
       <c r="I46" t="n">
         <v>872.6458786654357</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K46" t="n">
-        <v>12.07</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="L46" t="n">
         <v>5.73</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>10.45</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44893</v>
+        <v>44894</v>
       </c>
       <c r="H47" t="n">
-        <v>854.05</v>
+        <v>865.65</v>
       </c>
       <c r="I47" t="n">
         <v>863.2996348885356</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K47" t="n">
-        <v>2.03</v>
+        <v>0.7</v>
       </c>
       <c r="L47" t="n">
         <v>5.65</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>6.18</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45043</v>
+        <v>45044</v>
       </c>
       <c r="H48" t="n">
-        <v>953.6</v>
+        <v>907.5</v>
       </c>
       <c r="I48" t="n">
         <v>939.4637725452649</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K48" t="n">
-        <v>10.16</v>
+        <v>4.83</v>
       </c>
       <c r="L48" t="n">
         <v>1.49</v>
       </c>
       <c r="M48" t="n">
-        <v>1.14</v>
+        <v>2.16</v>
       </c>
       <c r="N48" t="n">
-        <v>3.06</v>
+        <v>4.83</v>
       </c>
       <c r="O48" t="n">
         <v>1.36</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>6</v>
+      </c>
+      <c r="U48" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>9.19</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45057</v>
+        <v>45058</v>
       </c>
       <c r="H49" t="n">
-        <v>982.6</v>
+        <v>999.2</v>
       </c>
       <c r="I49" t="n">
         <v>987.3454419497466</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K49" t="n">
-        <v>-8.279999999999999</v>
+        <v>-10.1</v>
       </c>
       <c r="L49" t="n">
-        <v>8.98</v>
+        <v>10.61</v>
       </c>
       <c r="M49" t="n">
         <v>2.34</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.59</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45145</v>
+        <v>45146</v>
       </c>
       <c r="H50" t="n">
-        <v>1030.7</v>
+        <v>1009.45</v>
       </c>
       <c r="I50" t="n">
         <v>1011.526867101744</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K50" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="L50" t="n">
         <v>2.18</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>7.66</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45232</v>
+        <v>45233</v>
       </c>
       <c r="H51" t="n">
-        <v>991.15</v>
+        <v>1020.7</v>
       </c>
       <c r="I51" t="n">
         <v>1018.537399370921</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K51" t="n">
-        <v>1.81</v>
+        <v>-1.11</v>
       </c>
       <c r="L51" t="n">
         <v>3.82</v>
@@ -3348,7 +3959,7 @@
         <v>2.81</v>
       </c>
       <c r="N51" t="n">
-        <v>2.43</v>
+        <v>2.98</v>
       </c>
       <c r="O51" t="n">
         <v>-2.06</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.02</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45307</v>
+        <v>45308</v>
       </c>
       <c r="H52" t="n">
-        <v>1122.8</v>
+        <v>1100.5</v>
       </c>
       <c r="I52" t="n">
         <v>1121.653974821236</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K52" t="n">
-        <v>10</v>
+        <v>7.82</v>
       </c>
       <c r="L52" t="n">
         <v>4.55</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="H53" t="n">
-        <v>1164.2</v>
+        <v>1254.55</v>
       </c>
       <c r="I53" t="n">
         <v>1187.307249540913</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K53" t="n">
-        <v>-5.79</v>
+        <v>-14</v>
       </c>
       <c r="L53" t="n">
-        <v>7.31</v>
+        <v>19.43</v>
       </c>
       <c r="M53" t="n">
-        <v>1.55</v>
+        <v>4.11</v>
       </c>
       <c r="N53" t="n">
-        <v>4.11</v>
+        <v>7.76</v>
       </c>
       <c r="O53" t="n">
         <v>-1.99</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>10.01</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="H54" t="n">
-        <v>1189.4</v>
+        <v>1177.55</v>
       </c>
       <c r="I54" t="n">
         <v>1186.405540990406</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K54" t="n">
-        <v>-5.19</v>
+        <v>-6.14</v>
       </c>
       <c r="L54" t="n">
-        <v>6.34</v>
+        <v>6.48</v>
       </c>
       <c r="M54" t="n">
         <v>1.91</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>9.640000000000001</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45418</v>
+        <v>45419</v>
       </c>
       <c r="H55" t="n">
-        <v>1250.15</v>
+        <v>1322.35</v>
       </c>
       <c r="I55" t="n">
         <v>1261.429517806073</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K55" t="n">
-        <v>-6.17</v>
+        <v>-12.3</v>
       </c>
       <c r="L55" t="n">
-        <v>8.65</v>
+        <v>14.64</v>
       </c>
       <c r="M55" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="N55" t="n">
-        <v>2.98</v>
+        <v>5.78</v>
       </c>
       <c r="O55" t="n">
         <v>-1</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>9.93</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45517</v>
+        <v>45518</v>
       </c>
       <c r="H56" t="n">
-        <v>1388.5</v>
+        <v>1371.1</v>
       </c>
       <c r="I56" t="n">
         <v>1371.617902623158</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K56" t="n">
-        <v>5</v>
+        <v>3.69</v>
       </c>
       <c r="L56" t="n">
         <v>5.34</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H57" t="n">
-        <v>1492.05</v>
+        <v>1503.05</v>
       </c>
       <c r="I57" t="n">
         <v>1499.601132982337</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K57" t="n">
-        <v>-8.82</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="L57" t="n">
         <v>11.46</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>8.34</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45561</v>
+        <v>45562</v>
       </c>
       <c r="H58" t="n">
-        <v>1422.3</v>
+        <v>1388.65</v>
       </c>
       <c r="I58" t="n">
         <v>1398.663063234647</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K58" t="n">
-        <v>-5.37</v>
+        <v>-7.61</v>
       </c>
       <c r="L58" t="n">
-        <v>6.38</v>
+        <v>10.61</v>
       </c>
       <c r="M58" t="n">
         <v>1.03</v>
       </c>
       <c r="N58" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="O58" t="n">
         <v>0.74</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.86</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45660</v>
+        <v>45663</v>
       </c>
       <c r="H59" t="n">
-        <v>1116.65</v>
+        <v>1141.85</v>
       </c>
       <c r="I59" t="n">
         <v>1133.195847852309</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K59" t="n">
-        <v>19.59</v>
+        <v>17.77</v>
       </c>
       <c r="L59" t="n">
         <v>1.93</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>7.56</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45695</v>
+        <v>45698</v>
       </c>
       <c r="H60" t="n">
-        <v>1106.75</v>
+        <v>1091.25</v>
       </c>
       <c r="I60" t="n">
         <v>1094.507593402039</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.07</v>
+        <v>-4.43</v>
       </c>
       <c r="L60" t="n">
-        <v>4.14</v>
+        <v>5.42</v>
       </c>
       <c r="M60" t="n">
         <v>1.4</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>13.56</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="H61" t="n">
-        <v>1074.3</v>
+        <v>1101.5</v>
       </c>
       <c r="I61" t="n">
         <v>1086.145087260669</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K61" t="n">
-        <v>1.55</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L61" t="n">
         <v>7.22</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>9.34</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45820</v>
+        <v>45821</v>
       </c>
       <c r="H62" t="n">
-        <v>1203.9</v>
+        <v>1188.8</v>
       </c>
       <c r="I62" t="n">
         <v>1200.933849361585</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K62" t="n">
-        <v>9.300000000000001</v>
+        <v>7.93</v>
       </c>
       <c r="L62" t="n">
         <v>4.31</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>6.24</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45842</v>
+        <v>45845</v>
       </c>
       <c r="H63" t="n">
-        <v>1192.9</v>
+        <v>1268.4</v>
       </c>
       <c r="I63" t="n">
         <v>1234.611752350689</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.34</v>
+        <v>-6.7</v>
       </c>
       <c r="L63" t="n">
-        <v>1.43</v>
+        <v>6.99</v>
       </c>
       <c r="M63" t="n">
-        <v>0.85</v>
+        <v>2.71</v>
       </c>
       <c r="N63" t="n">
-        <v>1.85</v>
+        <v>6.33</v>
       </c>
       <c r="O63" t="n">
         <v>-1.25</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>7.92</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45866</v>
+        <v>45867</v>
       </c>
       <c r="H64" t="n">
-        <v>1215</v>
+        <v>1210.6</v>
       </c>
       <c r="I64" t="n">
         <v>1213.921332467098</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K64" t="n">
-        <v>-4.21</v>
+        <v>-4.56</v>
       </c>
       <c r="L64" t="n">
-        <v>4.94</v>
+        <v>5.22</v>
       </c>
       <c r="M64" t="n">
         <v>1.25</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>5.35</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="H65" t="n">
-        <v>1256.8</v>
+        <v>1283.8</v>
       </c>
       <c r="I65" t="n">
         <v>1275.332391803591</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.82</v>
+        <v>-6.05</v>
       </c>
       <c r="L65" t="n">
         <v>6.56</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H66" t="n">
-        <v>1189.2</v>
+        <v>1163.9</v>
       </c>
       <c r="I66" t="n">
         <v>1185.626610040243</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K66" t="n">
-        <v>-7.37</v>
+        <v>-9.34</v>
       </c>
       <c r="L66" t="n">
-        <v>8.539999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="M66" t="n">
         <v>0.54</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="H67" t="n">
-        <v>1118.6</v>
+        <v>1178.6</v>
       </c>
       <c r="I67" t="n">
         <v>1170.822000849199</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K67" t="n">
-        <v>3.89</v>
+        <v>-1.26</v>
       </c>
       <c r="L67" t="n">
         <v>2.16</v>
       </c>
       <c r="M67" t="n">
-        <v>0.49</v>
+        <v>2.63</v>
       </c>
       <c r="N67" t="n">
-        <v>1.18</v>
+        <v>5.36</v>
       </c>
       <c r="O67" t="n">
         <v>-2.13</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>7.66</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="H68" t="n">
-        <v>1240.4</v>
+        <v>1173.9</v>
       </c>
       <c r="I68" t="n">
         <v>1183.594343394054</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K68" t="n">
-        <v>5.24</v>
+        <v>-0.4</v>
       </c>
       <c r="L68" t="n">
         <v>6.05</v>
@@ -4317,7 +5132,7 @@
         <v>0.91</v>
       </c>
       <c r="N68" t="n">
-        <v>2.11</v>
+        <v>5.36</v>
       </c>
       <c r="O68" t="n">
         <v>5.36</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>8.77</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H69" t="n">
-        <v>1063.35</v>
+        <v>1078.1</v>
       </c>
       <c r="I69" t="n">
         <v>1076.772388412962</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K69" t="n">
-        <v>9.42</v>
+        <v>8.16</v>
       </c>
       <c r="L69" t="n">
         <v>5.66</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>10.27</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="H70" t="n">
-        <v>1094.1</v>
+        <v>1036.6</v>
       </c>
       <c r="I70" t="n">
         <v>1039.755177164268</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K70" t="n">
-        <v>1.48</v>
+        <v>-3.85</v>
       </c>
       <c r="L70" t="n">
-        <v>3.58</v>
+        <v>4.09</v>
       </c>
       <c r="M70" t="n">
-        <v>2.51</v>
+        <v>2.69</v>
       </c>
       <c r="N70" t="n">
-        <v>4.64</v>
+        <v>5.26</v>
       </c>
       <c r="O70" t="n">
         <v>1.39</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>11.74</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="H71" t="n">
-        <v>1043.6</v>
+        <v>1077.2</v>
       </c>
       <c r="I71" t="n">
         <v>1069.95512107303</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.68</v>
+        <v>-3.92</v>
       </c>
       <c r="L71" t="n">
-        <v>2.71</v>
+        <v>4.35</v>
       </c>
       <c r="M71" t="n">
         <v>1.3</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>8.51</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="H72" t="n">
-        <v>1025</v>
+        <v>910</v>
       </c>
       <c r="I72" t="n">
         <v>1017.957479675481</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K72" t="n">
-        <v>-4.85</v>
+        <v>-15.52</v>
       </c>
       <c r="L72" t="n">
-        <v>5.59</v>
+        <v>15.73</v>
       </c>
       <c r="M72" t="n">
-        <v>1.97</v>
+        <v>10</v>
       </c>
       <c r="N72" t="n">
-        <v>2.55</v>
+        <v>11.22</v>
       </c>
       <c r="O72" t="n">
         <v>3.22</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4605,6 +5480,14 @@
       <c r="Q73" t="n">
         <v>53</v>
       </c>
+      <c r="R73" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9563,7 +10446,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.9</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="6">
@@ -9573,7 +10456,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
@@ -9583,7 +10466,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8">
@@ -9593,7 +10476,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -9603,7 +10486,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -9613,7 +10496,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11">
@@ -9653,7 +10536,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="15">
@@ -9663,7 +10546,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.63</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="16">
@@ -9673,7 +10556,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.29</v>
+        <v>-3.23</v>
       </c>
     </row>
     <row r="17">
@@ -9683,7 +10566,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>46.66</v>
+        <v>46.24</v>
       </c>
     </row>
     <row r="18">
@@ -9693,7 +10576,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.1</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="19">
@@ -9703,7 +10586,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.35</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="20">
@@ -9713,7 +10596,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.85</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="21">
@@ -9723,7 +10606,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.32</v>
+        <v>19.43</v>
       </c>
     </row>
     <row r="22">
@@ -9733,7 +10616,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -9743,7 +10626,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -9753,7 +10636,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="25">
@@ -9763,7 +10646,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.91</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -9773,7 +10656,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.66</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="27">
@@ -9783,7 +10666,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.4</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="28">
@@ -9793,7 +10676,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29">
